--- a/education_forms/035_opinion_article_assessment_form--education_forms.xlsx
+++ b/education_forms/035_opinion_article_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>review_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Review Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>article_title</t>
+          <t>article_title_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Article Title</t>
+          <t>Article Title 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>recommendation_choices</t>
+          <t>article_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>blog_post</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Blog Post</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>blog_post</t>
+          <t>news_story</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blog Post</t>
+          <t>News Story</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>news_story</t>
+          <t>research_paper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>News Story</t>
+          <t>Research Paper</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>research_paper</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Research Paper</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>tutorial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Tutorial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>article_type_choices</t>
+          <t>recommended_for_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tutorial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>recommended_for_choices</t>
+          <t>review_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>book_review</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Book Review</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recommended_for_choices</t>
+          <t>review_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>movie_review</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Movie Review</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>book_review</t>
+          <t>product_review</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Book Review</t>
+          <t>Product Review</t>
         </is>
       </c>
     </row>
@@ -1488,44 +1488,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>movie_review</t>
+          <t>service_review</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Movie Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>review_type_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>product_review</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Product Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>review_type_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>service_review</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>Service Review</t>
         </is>
